--- a/Imports/Updated_Business_Cases.xlsx
+++ b/Imports/Updated_Business_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aq\ix\MartinDow\PartialSB-MartinDow\Imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9D4D43-B05C-481D-ACC2-5CBC93C9D696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A9F2B5-16E2-4584-B367-81C8EF7DC5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
